--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:20:05+00:00</t>
+    <t>2026-07-28T10:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:50:36+00:00</t>
+    <t>2026-07-29T08:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,13 +78,16 @@
     <t>Description</t>
   </si>
   <si>
-    <t>IDDSI food-axis texture levels 4–7 (SNOMED CT-embedded IDDSI concepts), for NutritionOrder.oralDiet.texture.modifier.</t>
+    <t>IDDSI food-axis texture levels 4–7 (SNOMED CT-embedded IDDSI concepts), for NutritionOrder.oralDiet.texture.modifier. The IDDSI food axis spans Levels 3–7; Level 3 (Liquidised) is the shared Moderately Thick concept and is not enumerated here, so it is reached through the extensible binding.</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Value-set definition: MIT (© 2026 N. Kapan Tunçer and S. Tunçer). Content is referenced, not redistributed: this value set enumerates third-party concept identifiers (SNOMED CT © SNOMED International; LOINC © Regenstrief Institute, Inc.; IDDSI framework CC BY-SA 4.0, used unmodified) and carries no display terms, which are supplied at expansion time by the implementer's own terminology server. Implementers must hold the applicable third-party licences.</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -353,14 +356,16 @@
       <c r="A13" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -379,7 +384,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>20</v>
@@ -387,31 +392,31 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2"/>
     </row>
@@ -425,10 +430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:35:16+00:00</t>
+    <t>2026-07-29T12:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:05:46+00:00</t>
+    <t>2026-07-31T09:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0</t>
+    <t>1.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:21:13+00:00</t>
+    <t>2026-08-13T14:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:00:50+00:00</t>
+    <t>2026-08-13T23:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.2</t>
+    <t>1.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T23:31:20+00:00</t>
+    <t>2026-08-14T00:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.3</t>
+    <t>1.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:08:39+00:00</t>
+    <t>2026-08-14T00:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.4</t>
+    <t>1.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T00:48:45+00:00</t>
+    <t>2026-08-15T14:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.5</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-15T14:40:00+00:00</t>
+    <t>2026-08-18T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.3.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T10:55:39+00:00</t>
+    <t>2026-08-18T13:05:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.1</t>
+    <t>1.3.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:05:08+00:00</t>
+    <t>2026-08-18T14:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-iddsi-food-levels.xlsx
+++ b/ValueSet-iddsi-food-levels.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.2</t>
+    <t>1.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T14:23:53+00:00</t>
+    <t>2026-08-19T10:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
